--- a/make_table/t1.xlsx
+++ b/make_table/t1.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>申请日期</t>
   </si>
@@ -54,321 +54,6 @@
   </si>
   <si>
     <t>是否完成退款</t>
-  </si>
-  <si>
-    <t>瑞丰</t>
-  </si>
-  <si>
-    <t>5111067926075068027</t>
-  </si>
-  <si>
-    <t>钦风识你</t>
-  </si>
-  <si>
-    <t>暂未寄出</t>
-  </si>
-  <si>
-    <t>4502302884105091802</t>
-  </si>
-  <si>
-    <t>js459649073</t>
-  </si>
-  <si>
-    <t>2128.77</t>
-  </si>
-  <si>
-    <t>腾伟</t>
-  </si>
-  <si>
-    <t>3297137523297135890</t>
-  </si>
-  <si>
-    <t>yuanjun28101</t>
-  </si>
-  <si>
-    <t>540.12</t>
-  </si>
-  <si>
-    <t>顺丰速运 SF5199883700753</t>
-  </si>
-  <si>
-    <t>0425物流未更新到潮州</t>
-  </si>
-  <si>
-    <t>5111041574957279923</t>
-  </si>
-  <si>
-    <t>我是凡大爷</t>
-  </si>
-  <si>
-    <t>1247.96</t>
-  </si>
-  <si>
-    <t>5110873239128008729</t>
-  </si>
-  <si>
-    <t>济南天才卜栀明</t>
-  </si>
-  <si>
-    <t>1277.97</t>
-  </si>
-  <si>
-    <t>顺丰速运 SF0217641150139</t>
-  </si>
-  <si>
-    <t>4502306269122023121</t>
-  </si>
-  <si>
-    <t>tb1335246221</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>顺丰速运 SF5199805348122</t>
-  </si>
-  <si>
-    <t>2701862583092037871</t>
-  </si>
-  <si>
-    <t>chenjil83239311</t>
-  </si>
-  <si>
-    <t>779.2</t>
-  </si>
-  <si>
-    <t>顺丰速运 SF5199653123158</t>
-  </si>
-  <si>
-    <t>0425物流已更新到潮州</t>
-  </si>
-  <si>
-    <t>是</t>
-  </si>
-  <si>
-    <t>2701862583168011853</t>
-  </si>
-  <si>
-    <t>tb95981780123</t>
-  </si>
-  <si>
-    <t>258.52</t>
-  </si>
-  <si>
-    <t>极兔速递 JT3160759084396</t>
-  </si>
-  <si>
-    <t>0424物流未更新到潮州</t>
-  </si>
-  <si>
-    <t>2701867911006002590</t>
-  </si>
-  <si>
-    <t>锦鲤peace</t>
-  </si>
-  <si>
-    <t>1399</t>
-  </si>
-  <si>
-    <t>顺丰速运 SF5130430037278</t>
-  </si>
-  <si>
-    <t>4502317068011023435</t>
-  </si>
-  <si>
-    <t>雨飘一季</t>
-  </si>
-  <si>
-    <t>113.72</t>
-  </si>
-  <si>
-    <t>申通快递 772060700049594</t>
-  </si>
-  <si>
-    <t>4502296837024046206</t>
-  </si>
-  <si>
-    <t>thzxlm</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>极兔速递 JT3160903068070</t>
-  </si>
-  <si>
-    <t>换货</t>
-  </si>
-  <si>
-    <t>2701859449173028370</t>
-  </si>
-  <si>
-    <t>董晓龙93</t>
-  </si>
-  <si>
-    <t>顺丰速运 SF5130702497702</t>
-  </si>
-  <si>
-    <t>0423物流未更新到潮州</t>
-  </si>
-  <si>
-    <t>2701861394120018984</t>
-  </si>
-  <si>
-    <t>t_1494908056584_0625</t>
-  </si>
-  <si>
-    <t>812.12</t>
-  </si>
-  <si>
-    <t>顺丰速运 SF5199054527984</t>
-  </si>
-  <si>
-    <t>梓越</t>
-  </si>
-  <si>
-    <t>2701863086005062494</t>
-  </si>
-  <si>
-    <t>至尊宝shao</t>
-  </si>
-  <si>
-    <t>顺丰速运 SF5199006074915</t>
-  </si>
-  <si>
-    <t>2701856894073000070</t>
-  </si>
-  <si>
-    <t>tb2872783</t>
-  </si>
-  <si>
-    <t>顺丰速运 SF5199068760476</t>
-  </si>
-  <si>
-    <t>4502318798045006230</t>
-  </si>
-  <si>
-    <t>蜡笔小新lllx</t>
-  </si>
-  <si>
-    <t>顺丰速运 SF5199015712505</t>
-  </si>
-  <si>
-    <t>2701853654087008594</t>
-  </si>
-  <si>
-    <t>tb106810475484</t>
-  </si>
-  <si>
-    <t>中通快递 73705035257149</t>
-  </si>
-  <si>
-    <t>0422物流未更新到潮州</t>
-  </si>
-  <si>
-    <t>2701859127046093066</t>
-  </si>
-  <si>
-    <t>毛毛7913</t>
-  </si>
-  <si>
-    <t>申通快递 772060523220122</t>
-  </si>
-  <si>
-    <t>2701841521072009065</t>
-  </si>
-  <si>
-    <t>账户注销中i</t>
-  </si>
-  <si>
-    <t>SF5199263188095</t>
-  </si>
-  <si>
-    <t>0421物流未更新到潮州</t>
-  </si>
-  <si>
-    <t>4502318186109018328</t>
-  </si>
-  <si>
-    <t>张尹赫</t>
-  </si>
-  <si>
-    <t>顺丰速运 SF5199208107519</t>
-  </si>
-  <si>
-    <t>4502265372069087501</t>
-  </si>
-  <si>
-    <t>tb55359442</t>
-  </si>
-  <si>
-    <t>772060602470173</t>
-  </si>
-  <si>
-    <t>2701854807114000465</t>
-  </si>
-  <si>
-    <t>庄勤滨</t>
-  </si>
-  <si>
-    <t>中通快递 73704919506227</t>
-  </si>
-  <si>
-    <t>0421物流已更新到潮州</t>
-  </si>
-  <si>
-    <t>4502302670020011839</t>
-  </si>
-  <si>
-    <t>jingjing1yuhe</t>
-  </si>
-  <si>
-    <t>中通快递 73704734226122</t>
-  </si>
-  <si>
-    <t>0420物流未更新到潮州</t>
-  </si>
-  <si>
-    <t>2701831443174028763</t>
-  </si>
-  <si>
-    <t>weihua26685546</t>
-  </si>
-  <si>
-    <t>极兔速递 JT3160267097581</t>
-  </si>
-  <si>
-    <t>0420物流已更新到潮州</t>
-  </si>
-  <si>
-    <t>2701834034063019581</t>
-  </si>
-  <si>
-    <t>4502306269021127242</t>
-  </si>
-  <si>
-    <t>何瑞豪333</t>
-  </si>
-  <si>
-    <t>顺丰速运 SF0222053052953</t>
-  </si>
-  <si>
-    <t>4502302812049026735</t>
-  </si>
-  <si>
-    <t>tb451347254980</t>
-  </si>
-  <si>
-    <t>中通快递 73704724338426</t>
-  </si>
-  <si>
-    <t>4502280924002020507</t>
-  </si>
-  <si>
-    <t>月凉如水1983</t>
-  </si>
-  <si>
-    <t>申通快递 772060532356228</t>
   </si>
 </sst>
 </file>
@@ -1067,7 +752,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1116,27 +801,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1524,742 +1188,303 @@
       </c>
     </row>
     <row r="2" ht="15" spans="2:11">
-      <c r="B2" s="2">
-        <v>46137</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="6">
-        <v>943.8</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="5"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="4"/>
       <c r="I2" s="5"/>
       <c r="J2" s="7"/>
       <c r="K2" s="8"/>
     </row>
     <row r="3" ht="15" spans="2:11">
-      <c r="B3" s="2">
-        <v>46137</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="5"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
       <c r="I3" s="5"/>
       <c r="J3" s="7"/>
       <c r="K3" s="8"/>
     </row>
     <row r="4" ht="15" spans="2:11">
-      <c r="B4" s="2">
-        <v>46137</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>21</v>
-      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="5"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="5"/>
       <c r="J4" s="7"/>
       <c r="K4" s="8"/>
     </row>
     <row r="5" ht="15" spans="2:11">
-      <c r="B5" s="2">
-        <v>46137</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="5"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
       <c r="I5" s="5"/>
       <c r="J5" s="7"/>
       <c r="K5" s="8"/>
     </row>
     <row r="6" ht="15" spans="2:11">
-      <c r="B6" s="2">
-        <v>46137</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>21</v>
-      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="5"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="5"/>
       <c r="J6" s="7"/>
       <c r="K6" s="8"/>
     </row>
     <row r="7" spans="2:11">
-      <c r="B7" s="2">
-        <v>46137</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>21</v>
-      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="5"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="5"/>
       <c r="J7" s="7"/>
       <c r="K7" s="10"/>
     </row>
     <row r="8" ht="15" spans="2:11">
-      <c r="B8" s="11">
-        <v>46136</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="I8" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="J8" s="15" t="s">
-        <v>38</v>
-      </c>
+      <c r="B8" s="11"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="14"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="15"/>
       <c r="K8" s="8"/>
     </row>
     <row r="9" spans="2:11">
-      <c r="B9" s="2">
-        <v>46136</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>43</v>
-      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="5"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="5"/>
       <c r="J9" s="7"/>
     </row>
     <row r="10" spans="2:11">
-      <c r="B10" s="2">
-        <v>46136</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>43</v>
-      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="5"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="5"/>
       <c r="J10" s="7"/>
     </row>
     <row r="11" spans="2:11">
-      <c r="B11" s="2">
-        <v>46136</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>43</v>
-      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="5"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="5"/>
       <c r="J11" s="7"/>
     </row>
     <row r="12" spans="2:11">
-      <c r="B12" s="2">
-        <v>46135</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>56</v>
-      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="5"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="7"/>
     </row>
     <row r="13" spans="2:11">
-      <c r="B13" s="11">
-        <v>46135</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="I13" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="J13" s="15" t="s">
-        <v>38</v>
-      </c>
+      <c r="B13" s="11"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="14"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="15"/>
     </row>
     <row r="14" spans="2:11">
-      <c r="B14" s="11">
-        <v>46135</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="I14" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="J14" s="15" t="s">
-        <v>38</v>
-      </c>
+      <c r="B14" s="11"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="15"/>
     </row>
     <row r="15" spans="2:11">
-      <c r="B15" s="11">
-        <v>46134</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="G15" s="16">
-        <v>212.19</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="I15" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="J15" s="15" t="s">
-        <v>38</v>
-      </c>
+      <c r="B15" s="11"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="14"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="15"/>
     </row>
     <row r="16" spans="2:11">
-      <c r="B16" s="11">
-        <v>46134</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E16" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="G16" s="16">
-        <v>1112.66</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="I16" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="J16" s="15" t="s">
-        <v>38</v>
-      </c>
+      <c r="B16" s="11"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="14"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="15"/>
     </row>
     <row r="17" spans="2:12">
-      <c r="B17" s="11">
-        <v>46134</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="G17" s="16">
-        <v>296.77</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="I17" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="J17" s="15" t="s">
-        <v>38</v>
-      </c>
+      <c r="B17" s="11"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="14"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="15"/>
     </row>
     <row r="18" spans="2:12">
-      <c r="B18" s="11">
-        <v>46134</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="G18" s="16">
-        <v>3912.17</v>
-      </c>
-      <c r="H18" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="I18" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="J18" s="15" t="s">
-        <v>38</v>
-      </c>
+      <c r="B18" s="11"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="14"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="15"/>
     </row>
     <row r="19" spans="2:12">
-      <c r="B19" s="2">
-        <v>46133</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="G19" s="6">
-        <v>834</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>78</v>
-      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="5"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="5"/>
       <c r="J19" s="7"/>
     </row>
     <row r="20" spans="2:12">
-      <c r="B20" s="11">
-        <v>46133</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="E20" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="G20" s="16">
-        <v>814.62</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="I20" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="J20" s="15" t="s">
-        <v>38</v>
-      </c>
+      <c r="B20" s="11"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="14"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="15"/>
     </row>
     <row r="21" spans="2:12">
-      <c r="B21" s="11">
-        <v>46133</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="E21" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="G21" s="16">
-        <v>1292.17</v>
-      </c>
-      <c r="H21" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="I21" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="J21" s="15" t="s">
-        <v>38</v>
-      </c>
+      <c r="B21" s="11"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="14"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="15"/>
     </row>
     <row r="22" spans="2:12">
-      <c r="B22" s="11">
-        <v>46133</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="E22" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="G22" s="16">
-        <v>1284.2</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="I22" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="J22" s="15" t="s">
-        <v>38</v>
-      </c>
+      <c r="B22" s="11"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="14"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="15"/>
     </row>
     <row r="23" spans="2:12">
-      <c r="B23" s="11">
-        <v>46132</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="G23" s="16">
-        <v>940.21</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="I23" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="J23" s="15" t="s">
-        <v>38</v>
-      </c>
+      <c r="B23" s="11"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="14"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="15"/>
     </row>
     <row r="24" spans="2:12">
-      <c r="B24" s="11">
-        <v>46132</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="E24" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="G24" s="16">
-        <v>105.82</v>
-      </c>
-      <c r="H24" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="I24" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="J24" s="15" t="s">
-        <v>38</v>
-      </c>
+      <c r="B24" s="11"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="14"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="15"/>
     </row>
     <row r="25" spans="2:12">
-      <c r="B25" s="11">
-        <v>46131</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="E25" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="G25" s="16">
-        <v>288.64</v>
-      </c>
-      <c r="H25" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="I25" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="J25" s="15" t="s">
-        <v>38</v>
-      </c>
+      <c r="B25" s="11"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="14"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="15"/>
     </row>
     <row r="26" spans="2:12">
-      <c r="B26" s="11">
-        <v>46131</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="E26" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="G26" s="17">
-        <v>799</v>
-      </c>
-      <c r="H26" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="I26" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="J26" s="15" t="s">
-        <v>38</v>
-      </c>
+      <c r="B26" s="11"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="14"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="15"/>
     </row>
     <row r="27" spans="2:12">
-      <c r="B27" s="11">
-        <v>46131</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="E27" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="G27" s="17">
-        <v>260.4</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="I27" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="J27" s="15" t="s">
-        <v>38</v>
-      </c>
+      <c r="B27" s="11"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="14"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="15"/>
     </row>
     <row r="28" spans="2:12">
-      <c r="B28" s="11">
-        <v>46131</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="E28" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="G28" s="16">
-        <v>1093.29</v>
-      </c>
-      <c r="H28" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="I28" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="J28" s="15" t="s">
-        <v>38</v>
-      </c>
+      <c r="B28" s="11"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="14"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="15"/>
     </row>
     <row r="29" spans="2:12">
-      <c r="B29" s="11">
-        <v>46131</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="E29" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="G29" s="16">
-        <v>301.3</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="I29" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="J29" s="15" t="s">
-        <v>38</v>
-      </c>
+      <c r="B29" s="11"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="14"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="15"/>
     </row>
     <row r="30" ht="15" spans="2:12">
-      <c r="B30" s="18">
-        <v>46133</v>
-      </c>
-      <c r="C30" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="D30" s="20" t="s">
-        <v>111</v>
-      </c>
-      <c r="E30" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="F30"/>
-      <c r="G30" s="22">
-        <v>0</v>
-      </c>
-      <c r="H30" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="I30" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J30" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="K30" s="24"/>
-      <c r="L30" s="25"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="14"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="15"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/make_table/t1.xlsx
+++ b/make_table/t1.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>申请日期</t>
   </si>
@@ -54,6 +54,51 @@
   </si>
   <si>
     <t>是否完成退款</t>
+  </si>
+  <si>
+    <t>腾伟</t>
+  </si>
+  <si>
+    <t>4502296837024046206</t>
+  </si>
+  <si>
+    <t>thzxlm</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>极兔速递 JT3160903068070</t>
+  </si>
+  <si>
+    <t>0426物流已更新到潮州</t>
+  </si>
+  <si>
+    <t>换货</t>
+  </si>
+  <si>
+    <t>瑞丰</t>
+  </si>
+  <si>
+    <t>2701828489124026663</t>
+  </si>
+  <si>
+    <t>宜春邹志明</t>
+  </si>
+  <si>
+    <t>极兔速递 JT3159498098520</t>
+  </si>
+  <si>
+    <t>0414物流未更新到潮州</t>
+  </si>
+  <si>
+    <t>是</t>
+  </si>
+  <si>
+    <t>73704218931851</t>
+  </si>
+  <si>
+    <t>0419物流已更新到潮州</t>
   </si>
 </sst>
 </file>
@@ -102,12 +147,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FFFF4400"/>
-      <name val="PingFang SC"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei"/>
@@ -131,6 +170,13 @@
       <color rgb="FF000000"/>
       <name val="PingFang SC"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
@@ -752,7 +798,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -769,41 +815,49 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="176" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1152,13 +1206,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B1:L30"/>
+  <dimension ref="B1:L12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="10.7777777777778"/>
+    <col min="4" max="4" width="19.4444444444444" customWidth="1"/>
+    <col min="5" max="5" width="11.2222222222222" customWidth="1"/>
+    <col min="8" max="8" width="23.8888888888889" customWidth="1"/>
+    <col min="9" max="9" width="22.1111111111111" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11">
+    <row r="1" customHeight="1" spans="2:12">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1187,306 +1245,168 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="15" spans="2:11">
-      <c r="B2" s="2"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="5"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="8"/>
+    <row r="2" ht="15" spans="2:12">
+      <c r="B2" s="2">
+        <v>46135</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="7"/>
     </row>
-    <row r="3" ht="15" spans="2:11">
-      <c r="B3" s="2"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="5"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="8"/>
+    <row r="3" spans="2:12">
+      <c r="B3" s="8">
+        <v>46125</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="12">
+        <v>838</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="11"/>
     </row>
-    <row r="4" ht="15" spans="2:11">
-      <c r="B4" s="2"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="5"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="8"/>
+    <row r="4" spans="2:12">
+      <c r="B4" s="8"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="11"/>
+      <c r="G4" s="12">
+        <v>838</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" s="13"/>
+      <c r="L4" s="11"/>
     </row>
-    <row r="5" ht="15" spans="2:11">
-      <c r="B5" s="2"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="5"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="8"/>
+    <row r="5" spans="2:12">
+      <c r="B5" s="15"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="11"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="18"/>
     </row>
-    <row r="6" ht="15" spans="2:11">
-      <c r="B6" s="2"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="5"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="8"/>
+    <row r="6" spans="2:12">
+      <c r="B6" s="15"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="11"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="18"/>
     </row>
-    <row r="7" spans="2:11">
-      <c r="B7" s="2"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="5"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="10"/>
+    <row r="7" spans="2:12">
+      <c r="B7" s="15"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="11"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="18"/>
     </row>
-    <row r="8" ht="15" spans="2:11">
-      <c r="B8" s="11"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="14"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="8"/>
+    <row r="8" spans="2:12">
+      <c r="B8" s="15"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="11"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="18"/>
     </row>
-    <row r="9" spans="2:11">
-      <c r="B9" s="2"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="5"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="7"/>
+    <row r="9" spans="2:12">
+      <c r="B9" s="15"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="11"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="18"/>
     </row>
-    <row r="10" spans="2:11">
-      <c r="B10" s="2"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="5"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="7"/>
+    <row r="10" spans="2:12">
+      <c r="B10" s="15"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="11"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="18"/>
     </row>
-    <row r="11" spans="2:11">
-      <c r="B11" s="2"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="5"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="7"/>
+    <row r="11" spans="2:12">
+      <c r="B11" s="15"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="11"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="18"/>
     </row>
-    <row r="12" spans="2:11">
-      <c r="B12" s="2"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="5"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="7"/>
-    </row>
-    <row r="13" spans="2:11">
-      <c r="B13" s="11"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="14"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="15"/>
-    </row>
-    <row r="14" spans="2:11">
-      <c r="B14" s="11"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="15"/>
-    </row>
-    <row r="15" spans="2:11">
-      <c r="B15" s="11"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="14"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="15"/>
-    </row>
-    <row r="16" spans="2:11">
-      <c r="B16" s="11"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="14"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="15"/>
-    </row>
-    <row r="17" spans="2:12">
-      <c r="B17" s="11"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="14"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="15"/>
-    </row>
-    <row r="18" spans="2:12">
-      <c r="B18" s="11"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="14"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="15"/>
-    </row>
-    <row r="19" spans="2:12">
-      <c r="B19" s="2"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="5"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="7"/>
-    </row>
-    <row r="20" spans="2:12">
-      <c r="B20" s="11"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="14"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="15"/>
-    </row>
-    <row r="21" spans="2:12">
-      <c r="B21" s="11"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="14"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="14"/>
-      <c r="J21" s="15"/>
-    </row>
-    <row r="22" spans="2:12">
-      <c r="B22" s="11"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="14"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="14"/>
-      <c r="J22" s="15"/>
-    </row>
-    <row r="23" spans="2:12">
-      <c r="B23" s="11"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="14"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="15"/>
-    </row>
-    <row r="24" spans="2:12">
-      <c r="B24" s="11"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="14"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="15"/>
-    </row>
-    <row r="25" spans="2:12">
-      <c r="B25" s="11"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="14"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="14"/>
-      <c r="J25" s="15"/>
-    </row>
-    <row r="26" spans="2:12">
-      <c r="B26" s="11"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="14"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="15"/>
-    </row>
-    <row r="27" spans="2:12">
-      <c r="B27" s="11"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="14"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="14"/>
-      <c r="J27" s="15"/>
-    </row>
-    <row r="28" spans="2:12">
-      <c r="B28" s="11"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="14"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="14"/>
-      <c r="J28" s="15"/>
-    </row>
-    <row r="29" spans="2:12">
-      <c r="B29" s="11"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="14"/>
-      <c r="G29" s="16"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="14"/>
-      <c r="J29" s="15"/>
-    </row>
-    <row r="30" ht="15" spans="2:12">
-      <c r="B30" s="11"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="14"/>
-      <c r="G30" s="16"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="14"/>
-      <c r="J30" s="15"/>
-      <c r="K30" s="8"/>
-      <c r="L30" s="18"/>
+    <row r="12" ht="15" spans="2:12">
+      <c r="B12" s="15"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="11"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="18"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="20"/>
     </row>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="J3:J4"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/make_table/t1.xlsx
+++ b/make_table/t1.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="75">
   <si>
     <t>申请日期</t>
   </si>
@@ -59,46 +59,220 @@
     <t>腾伟</t>
   </si>
   <si>
-    <t>4502296837024046206</t>
-  </si>
-  <si>
-    <t>thzxlm</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>极兔速递 JT3160903068070</t>
-  </si>
-  <si>
-    <t>0426物流已更新到潮州</t>
-  </si>
-  <si>
-    <t>换货</t>
+    <t>3297901010220007689</t>
+  </si>
+  <si>
+    <t>花花花啊啊m</t>
+  </si>
+  <si>
+    <t>暂未寄出</t>
+  </si>
+  <si>
+    <t>5112077292914061845</t>
+  </si>
+  <si>
+    <t>bry168</t>
+  </si>
+  <si>
+    <t>3298257517445020082</t>
+  </si>
+  <si>
+    <t>跨海_高速</t>
+  </si>
+  <si>
+    <t>申通快递 772061046443705</t>
+  </si>
+  <si>
+    <t>0428物流未更新到潮州</t>
+  </si>
+  <si>
+    <t>5111854671699037843</t>
+  </si>
+  <si>
+    <t>旧金山0121</t>
+  </si>
+  <si>
+    <t>顺丰速运 SF0221623837115</t>
   </si>
   <si>
     <t>瑞丰</t>
   </si>
   <si>
-    <t>2701828489124026663</t>
-  </si>
-  <si>
-    <t>宜春邹志明</t>
-  </si>
-  <si>
-    <t>极兔速递 JT3159498098520</t>
-  </si>
-  <si>
-    <t>0414物流未更新到潮州</t>
+    <t>5112421778175023237</t>
+  </si>
+  <si>
+    <t>zhuoyingpeng</t>
+  </si>
+  <si>
+    <t>顺丰速运，SF0228083759096</t>
+  </si>
+  <si>
+    <t>0427物流未更新到潮州</t>
   </si>
   <si>
     <t>是</t>
   </si>
   <si>
-    <t>73704218931851</t>
-  </si>
-  <si>
-    <t>0419物流已更新到潮州</t>
+    <t>3298694232944009978</t>
+  </si>
+  <si>
+    <t>tb062516175225</t>
+  </si>
+  <si>
+    <t>极兔速递 JT5480183168323</t>
+  </si>
+  <si>
+    <t>振鸿</t>
+  </si>
+  <si>
+    <t>3297697322235106367</t>
+  </si>
+  <si>
+    <t>只能一年改一次</t>
+  </si>
+  <si>
+    <t>顺丰速运 SF0225523824581</t>
+  </si>
+  <si>
+    <t>5111273016030019324</t>
+  </si>
+  <si>
+    <t>jay_89757</t>
+  </si>
+  <si>
+    <t>顺丰速运 SF0226053710872</t>
+  </si>
+  <si>
+    <t>0427物流已更新到潮州</t>
+  </si>
+  <si>
+    <t>3297183962088001079</t>
+  </si>
+  <si>
+    <t>淡杰橙</t>
+  </si>
+  <si>
+    <t>申通快递 772061019165423</t>
+  </si>
+  <si>
+    <t>3297702000559001192</t>
+  </si>
+  <si>
+    <t>瞳孔中的水平线</t>
+  </si>
+  <si>
+    <t>中通快递 73705853678251</t>
+  </si>
+  <si>
+    <t>4502308394121050815</t>
+  </si>
+  <si>
+    <t>青晕晕</t>
+  </si>
+  <si>
+    <t>申通快递 772060951098059</t>
+  </si>
+  <si>
+    <t>3297897193516006882</t>
+  </si>
+  <si>
+    <t>黄昏光影</t>
+  </si>
+  <si>
+    <t>申通快递 772060984991552</t>
+  </si>
+  <si>
+    <r>
+      <t>5110974722843028333</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFDE3C36"/>
+        <rFont val="PingFang SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFDE3C36"/>
+        <rFont val="PingFang SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5111262469540028333</t>
+    </r>
+  </si>
+  <si>
+    <t>tantanjiadong</t>
+  </si>
+  <si>
+    <t>中通快递 73705800924611</t>
+  </si>
+  <si>
+    <t>5112015805018001926</t>
+  </si>
+  <si>
+    <t>卢卡娃11</t>
+  </si>
+  <si>
+    <t>顺丰速运 SF0229073694555</t>
+  </si>
+  <si>
+    <t>5111825688852085536</t>
+  </si>
+  <si>
+    <t>ckun00</t>
+  </si>
+  <si>
+    <t>中通快递 73705705478584</t>
+  </si>
+  <si>
+    <t>4502307746172039543</t>
+  </si>
+  <si>
+    <t>tb980163199765</t>
+  </si>
+  <si>
+    <t>顺丰速运 SF5131203810768</t>
+  </si>
+  <si>
+    <t>5111460397495097805</t>
+  </si>
+  <si>
+    <t>memory123chen</t>
+  </si>
+  <si>
+    <t>申通快递 772060889377679</t>
+  </si>
+  <si>
+    <t>4502307243092031121</t>
+  </si>
+  <si>
+    <t>t_1500087239816_0842</t>
+  </si>
+  <si>
+    <t>5111067926075068027</t>
+  </si>
+  <si>
+    <t>钦风识你</t>
+  </si>
+  <si>
+    <t>顺丰速运 SF0227613669644</t>
+  </si>
+  <si>
+    <t>4502302884105091802</t>
+  </si>
+  <si>
+    <t>js459649073</t>
+  </si>
+  <si>
+    <t>2128.77</t>
+  </si>
+  <si>
+    <t>申通快递 772060851430833</t>
   </si>
 </sst>
 </file>
@@ -147,36 +321,35 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FFFF4400"/>
+      <name val="PingFang SC"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="PingFang SC"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
@@ -798,7 +971,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -815,49 +988,81 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1206,7 +1411,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B1:L12"/>
+  <dimension ref="B1:L51"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="10.7777777777778"/>
@@ -1247,7 +1452,7 @@
     </row>
     <row r="2" ht="15" spans="2:12">
       <c r="B2" s="2">
-        <v>46135</v>
+        <v>46140</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>9</v>
@@ -1258,155 +1463,847 @@
       <c r="E2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="F2"/>
+      <c r="G2" s="6">
+        <v>694.2</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="5"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="8"/>
+    </row>
+    <row r="3" ht="15" spans="2:12">
+      <c r="B3" s="2">
+        <v>46140</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="E3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="F3"/>
+      <c r="G3" s="6">
+        <v>205.12</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="5"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="9"/>
+    </row>
+    <row r="4" ht="15" spans="2:12">
+      <c r="B4" s="2">
+        <v>46140</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="7"/>
-    </row>
-    <row r="3" spans="2:12">
-      <c r="B3" s="8">
-        <v>46125</v>
-      </c>
-      <c r="C3" s="9" t="s">
+      <c r="E4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="F4"/>
+      <c r="G4" s="6">
+        <v>103.14</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="I4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="12">
-        <v>838</v>
-      </c>
-      <c r="H3" s="12" t="s">
+      <c r="J4" s="7"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="9"/>
+    </row>
+    <row r="5" ht="15" spans="2:12">
+      <c r="B5" s="2">
+        <v>46140</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="E5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="13" t="s">
+      <c r="F5"/>
+      <c r="G5" s="6">
+        <v>1284</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="L3" s="11"/>
-    </row>
-    <row r="4" spans="2:12">
-      <c r="B4" s="8"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="11"/>
-      <c r="G4" s="12">
-        <v>838</v>
-      </c>
-      <c r="H4" s="14" t="s">
+      <c r="I5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="7"/>
+      <c r="K5" s="8"/>
+    </row>
+    <row r="6" ht="15" spans="2:12">
+      <c r="B6" s="2">
+        <v>46139</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="D6" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="13"/>
-      <c r="L4" s="11"/>
-    </row>
-    <row r="5" spans="2:12">
-      <c r="B5" s="15"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="11"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="18"/>
-    </row>
-    <row r="6" spans="2:12">
-      <c r="B6" s="15"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="11"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="18"/>
-    </row>
-    <row r="7" spans="2:12">
-      <c r="B7" s="15"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="11"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="18"/>
-    </row>
-    <row r="8" spans="2:12">
-      <c r="B8" s="15"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="11"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="18"/>
-    </row>
-    <row r="9" spans="2:12">
-      <c r="B9" s="15"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="11"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="18"/>
-    </row>
-    <row r="10" spans="2:12">
-      <c r="B10" s="15"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="11"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="18"/>
-    </row>
-    <row r="11" spans="2:12">
-      <c r="B11" s="15"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="11"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="18"/>
+      <c r="E6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6"/>
+      <c r="G6" s="6">
+        <v>1299</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="K6" s="8"/>
+    </row>
+    <row r="7" ht="15" spans="2:12">
+      <c r="B7" s="2">
+        <v>46139</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7"/>
+      <c r="G7" s="6">
+        <v>1290.35</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7" s="7"/>
+      <c r="K7" s="8"/>
+    </row>
+    <row r="8" ht="15" spans="2:12">
+      <c r="B8" s="2">
+        <v>46139</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8"/>
+      <c r="G8" s="6">
+        <v>827.12</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" s="7"/>
+      <c r="K8" s="8"/>
+    </row>
+    <row r="9" ht="15" spans="2:12">
+      <c r="B9" s="2">
+        <v>46139</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9"/>
+      <c r="G9" s="6">
+        <v>214.4</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J9" s="7"/>
+      <c r="K9" s="8"/>
+    </row>
+    <row r="10" ht="15" spans="2:12">
+      <c r="B10" s="2">
+        <v>46139</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10"/>
+      <c r="G10" s="6">
+        <v>163.12</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" s="7"/>
+      <c r="K10" s="8"/>
+    </row>
+    <row r="11" ht="15" spans="2:12">
+      <c r="B11" s="2">
+        <v>46139</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11"/>
+      <c r="G11" s="6">
+        <v>159</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J11" s="7"/>
+      <c r="K11" s="8"/>
     </row>
     <row r="12" ht="15" spans="2:12">
-      <c r="B12" s="15"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="11"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="18"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="20"/>
+      <c r="B12" s="2">
+        <v>46139</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F12"/>
+      <c r="G12" s="6">
+        <v>821.34</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J12" s="7"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="12"/>
+    </row>
+    <row r="13" ht="15" spans="2:12">
+      <c r="B13" s="2">
+        <v>46138</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F13"/>
+      <c r="G13" s="6">
+        <v>250.14</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J13" s="7"/>
+      <c r="K13" s="8"/>
+    </row>
+    <row r="14" ht="22.8" spans="2:12">
+      <c r="B14" s="2">
+        <v>46138</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F14"/>
+      <c r="G14" s="6">
+        <v>2206.13</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J14" s="7"/>
+      <c r="K14" s="8"/>
+    </row>
+    <row r="15" ht="15" spans="2:12">
+      <c r="B15" s="2">
+        <v>46138</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15"/>
+      <c r="G15" s="6">
+        <v>1037.2</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J15" s="7"/>
+      <c r="K15" s="8"/>
+    </row>
+    <row r="16" spans="2:12">
+      <c r="B16" s="13">
+        <v>46138</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="F16"/>
+      <c r="G16" s="17">
+        <v>929</v>
+      </c>
+      <c r="H16" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="I16" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="J16" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="K16" s="19"/>
+    </row>
+    <row r="17" ht="15" spans="2:11">
+      <c r="B17" s="2">
+        <v>46138</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F17"/>
+      <c r="G17" s="6">
+        <v>2799</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J17" s="7"/>
+      <c r="K17" s="8"/>
+    </row>
+    <row r="18" spans="2:11">
+      <c r="B18" s="13">
+        <v>46138</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="F18"/>
+      <c r="G18" s="17">
+        <v>165</v>
+      </c>
+      <c r="H18" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="I18" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="J18" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="K18" s="19"/>
+    </row>
+    <row r="19" ht="15" spans="2:11">
+      <c r="B19" s="2">
+        <v>46137</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F19"/>
+      <c r="G19" s="6">
+        <v>164.4</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I19" s="5"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="8"/>
+    </row>
+    <row r="20" ht="15" spans="2:11">
+      <c r="B20" s="2">
+        <v>46137</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F20"/>
+      <c r="G20" s="6">
+        <v>943.8</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J20" s="7"/>
+      <c r="K20" s="8"/>
+    </row>
+    <row r="21" ht="15" spans="2:11">
+      <c r="B21" s="2">
+        <v>46137</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F21"/>
+      <c r="G21" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J21" s="7"/>
+      <c r="K21" s="8"/>
+    </row>
+    <row r="22" ht="15" spans="2:11">
+      <c r="B22" s="20"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="23"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="23"/>
+      <c r="J22" s="24"/>
+      <c r="K22" s="25"/>
+    </row>
+    <row r="23" spans="2:11">
+      <c r="B23" s="26"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="9"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="29"/>
+      <c r="K23" s="30"/>
+    </row>
+    <row r="24" spans="2:11">
+      <c r="B24" s="26"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="9"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="29"/>
+      <c r="K24" s="30"/>
+    </row>
+    <row r="25" spans="2:11">
+      <c r="B25" s="26"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="9"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="29"/>
+      <c r="K25" s="30"/>
+    </row>
+    <row r="26" spans="2:11">
+      <c r="B26" s="26"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="9"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="29"/>
+      <c r="K26" s="30"/>
+    </row>
+    <row r="27" spans="2:11">
+      <c r="B27" s="26"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="9"/>
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="29"/>
+      <c r="K27" s="30"/>
+    </row>
+    <row r="28" ht="15" spans="2:11">
+      <c r="B28" s="26"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="9"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="29"/>
+      <c r="K28" s="25"/>
+    </row>
+    <row r="29" ht="15" spans="2:11">
+      <c r="B29" s="26"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="29"/>
+      <c r="K29" s="25"/>
+    </row>
+    <row r="30" spans="2:11">
+      <c r="B30" s="26"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="9"/>
+      <c r="G30" s="31"/>
+      <c r="H30" s="28"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="29"/>
+      <c r="K30" s="30"/>
+    </row>
+    <row r="31" spans="2:11">
+      <c r="B31" s="26"/>
+      <c r="C31" s="27"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="9"/>
+      <c r="G31" s="31"/>
+      <c r="H31" s="28"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="29"/>
+      <c r="K31" s="30"/>
+    </row>
+    <row r="32" spans="2:11">
+      <c r="B32" s="26"/>
+      <c r="C32" s="27"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="9"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="29"/>
+      <c r="K32" s="30"/>
+    </row>
+    <row r="33" spans="2:11">
+      <c r="B33" s="26"/>
+      <c r="C33" s="27"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="9"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="28"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="29"/>
+      <c r="K33" s="30"/>
+    </row>
+    <row r="34" spans="2:11">
+      <c r="B34" s="26"/>
+      <c r="C34" s="27"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="9"/>
+      <c r="G34" s="31"/>
+      <c r="H34" s="28"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="29"/>
+      <c r="K34" s="30"/>
+    </row>
+    <row r="35" spans="2:11">
+      <c r="B35" s="26"/>
+      <c r="C35" s="27"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="9"/>
+      <c r="G35" s="31"/>
+      <c r="H35" s="28"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="29"/>
+      <c r="K35" s="30"/>
+    </row>
+    <row r="36" ht="15" spans="2:11">
+      <c r="B36" s="26"/>
+      <c r="C36" s="27"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="9"/>
+      <c r="G36" s="31"/>
+      <c r="H36" s="28"/>
+      <c r="I36" s="9"/>
+      <c r="J36" s="29"/>
+      <c r="K36" s="25"/>
+    </row>
+    <row r="37" ht="15" spans="2:11">
+      <c r="B37" s="26"/>
+      <c r="C37" s="27"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="9"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="29"/>
+      <c r="K37" s="25"/>
+    </row>
+    <row r="38" ht="15" spans="2:11">
+      <c r="B38" s="26"/>
+      <c r="C38" s="27"/>
+      <c r="D38" s="28"/>
+      <c r="E38" s="9"/>
+      <c r="G38" s="31"/>
+      <c r="H38" s="28"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="29"/>
+      <c r="K38" s="25"/>
+    </row>
+    <row r="39" spans="2:11">
+      <c r="B39" s="26"/>
+      <c r="C39" s="27"/>
+      <c r="D39" s="28"/>
+      <c r="E39" s="9"/>
+      <c r="G39" s="31"/>
+      <c r="H39" s="28"/>
+      <c r="I39" s="9"/>
+      <c r="J39" s="29"/>
+      <c r="K39" s="30"/>
+    </row>
+    <row r="40" ht="15" spans="2:11">
+      <c r="B40" s="26"/>
+      <c r="C40" s="27"/>
+      <c r="D40" s="28"/>
+      <c r="E40" s="9"/>
+      <c r="G40" s="31"/>
+      <c r="H40" s="28"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="29"/>
+      <c r="K40" s="25"/>
+    </row>
+    <row r="41" ht="15" spans="2:11">
+      <c r="B41" s="26"/>
+      <c r="C41" s="27"/>
+      <c r="D41" s="28"/>
+      <c r="E41" s="9"/>
+      <c r="G41" s="31"/>
+      <c r="H41" s="28"/>
+      <c r="I41" s="9"/>
+      <c r="J41" s="29"/>
+      <c r="K41" s="25"/>
+    </row>
+    <row r="42" ht="15" spans="2:11">
+      <c r="B42" s="26"/>
+      <c r="C42" s="27"/>
+      <c r="D42" s="28"/>
+      <c r="E42" s="9"/>
+      <c r="G42" s="31"/>
+      <c r="H42" s="28"/>
+      <c r="I42" s="9"/>
+      <c r="J42" s="29"/>
+      <c r="K42" s="25"/>
+    </row>
+    <row r="43" spans="2:11">
+      <c r="B43" s="26"/>
+      <c r="C43" s="27"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="9"/>
+      <c r="G43" s="31"/>
+      <c r="H43" s="28"/>
+      <c r="I43" s="9"/>
+      <c r="J43" s="29"/>
+      <c r="K43" s="30"/>
+    </row>
+    <row r="44" spans="2:11">
+      <c r="B44" s="26"/>
+      <c r="C44" s="27"/>
+      <c r="D44" s="28"/>
+      <c r="E44" s="9"/>
+      <c r="G44" s="31"/>
+      <c r="H44" s="28"/>
+      <c r="I44" s="9"/>
+      <c r="J44" s="29"/>
+      <c r="K44" s="30"/>
+    </row>
+    <row r="45" ht="15" spans="2:11">
+      <c r="B45" s="26"/>
+      <c r="C45" s="27"/>
+      <c r="D45" s="28"/>
+      <c r="E45" s="9"/>
+      <c r="G45" s="32"/>
+      <c r="H45" s="28"/>
+      <c r="I45" s="9"/>
+      <c r="J45" s="29"/>
+      <c r="K45" s="25"/>
+    </row>
+    <row r="46" ht="15" spans="2:11">
+      <c r="B46" s="26"/>
+      <c r="C46" s="27"/>
+      <c r="D46" s="28"/>
+      <c r="E46" s="9"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="28"/>
+      <c r="I46" s="9"/>
+      <c r="J46" s="29"/>
+      <c r="K46" s="25"/>
+    </row>
+    <row r="47" spans="2:11">
+      <c r="B47" s="26"/>
+      <c r="C47" s="27"/>
+      <c r="D47" s="28"/>
+      <c r="E47" s="9"/>
+      <c r="G47" s="31"/>
+      <c r="H47" s="28"/>
+      <c r="I47" s="9"/>
+      <c r="J47" s="29"/>
+      <c r="K47" s="30"/>
+    </row>
+    <row r="48" spans="2:11">
+      <c r="B48" s="26"/>
+      <c r="C48" s="27"/>
+      <c r="D48" s="28"/>
+      <c r="E48" s="9"/>
+      <c r="G48" s="31"/>
+      <c r="H48" s="28"/>
+      <c r="I48" s="9"/>
+      <c r="J48" s="29"/>
+      <c r="K48" s="30"/>
+    </row>
+    <row r="49" spans="2:11">
+      <c r="B49" s="26"/>
+      <c r="C49" s="27"/>
+      <c r="D49" s="28"/>
+      <c r="E49" s="9"/>
+      <c r="G49" s="31"/>
+      <c r="H49" s="28"/>
+      <c r="I49" s="9"/>
+      <c r="J49" s="29"/>
+      <c r="K49" s="30"/>
+    </row>
+    <row r="50" ht="15" spans="2:11">
+      <c r="B50" s="26"/>
+      <c r="C50" s="27"/>
+      <c r="D50" s="28"/>
+      <c r="E50" s="9"/>
+      <c r="G50" s="31"/>
+      <c r="H50" s="28"/>
+      <c r="I50" s="9"/>
+      <c r="J50" s="29"/>
+      <c r="K50" s="25"/>
+    </row>
+    <row r="51" spans="2:11">
+      <c r="B51" s="26"/>
+      <c r="C51" s="27"/>
+      <c r="D51" s="28"/>
+      <c r="E51" s="9"/>
+      <c r="G51" s="31"/>
+      <c r="H51" s="28"/>
+      <c r="I51" s="9"/>
+      <c r="J51" s="29"/>
+      <c r="K51" s="30"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="J3:J4"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/make_table/t1.xlsx
+++ b/make_table/t1.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="120">
   <si>
     <t>申请日期</t>
   </si>
@@ -59,131 +59,104 @@
     <t>腾伟</t>
   </si>
   <si>
-    <t>3297901010220007689</t>
-  </si>
-  <si>
-    <t>花花花啊啊m</t>
-  </si>
-  <si>
-    <t>暂未寄出</t>
-  </si>
-  <si>
-    <t>5112077292914061845</t>
-  </si>
-  <si>
-    <t>bry168</t>
-  </si>
-  <si>
-    <t>3298257517445020082</t>
-  </si>
-  <si>
-    <t>跨海_高速</t>
-  </si>
-  <si>
-    <t>申通快递 772061046443705</t>
-  </si>
-  <si>
-    <t>0428物流未更新到潮州</t>
-  </si>
-  <si>
-    <t>5111854671699037843</t>
-  </si>
-  <si>
-    <t>旧金山0121</t>
-  </si>
-  <si>
-    <t>顺丰速运 SF0221623837115</t>
-  </si>
-  <si>
-    <t>瑞丰</t>
-  </si>
-  <si>
-    <t>5112421778175023237</t>
-  </si>
-  <si>
-    <t>zhuoyingpeng</t>
-  </si>
-  <si>
-    <t>顺丰速运，SF0228083759096</t>
-  </si>
-  <si>
-    <t>0427物流未更新到潮州</t>
+    <t>5111452335942020120</t>
+  </si>
+  <si>
+    <t>donghaiqiang19880726</t>
+  </si>
+  <si>
+    <t>申通快递 772061226028419</t>
+  </si>
+  <si>
+    <t>0430物流未更新到潮州</t>
+  </si>
+  <si>
+    <t>梓越</t>
+  </si>
+  <si>
+    <t>3297905761714027877</t>
+  </si>
+  <si>
+    <t>罗凯瑞1999</t>
+  </si>
+  <si>
+    <t>中通快递 73706275175725</t>
+  </si>
+  <si>
+    <t>3298624789787020998</t>
+  </si>
+  <si>
+    <t>快乐兔子999200</t>
+  </si>
+  <si>
+    <t>顺丰速运 SF0223964041105</t>
+  </si>
+  <si>
+    <t>5112623268640147926</t>
+  </si>
+  <si>
+    <t>yppno1</t>
+  </si>
+  <si>
+    <t>顺丰速运 SF5190341753928</t>
+  </si>
+  <si>
+    <t>5112453747049074013</t>
+  </si>
+  <si>
+    <t>哈哈嘻chm</t>
+  </si>
+  <si>
+    <t>顺丰速运 SF5131196350946</t>
+  </si>
+  <si>
+    <t>0429物流未更新到潮州</t>
+  </si>
+  <si>
+    <t>3298385497840145791</t>
+  </si>
+  <si>
+    <t>嘉合宝贝</t>
+  </si>
+  <si>
+    <t>中通快递 73706190057375</t>
+  </si>
+  <si>
+    <t>3298389531362044479</t>
+  </si>
+  <si>
+    <t>tb651964442493</t>
+  </si>
+  <si>
+    <t>SF5131022766781</t>
   </si>
   <si>
     <t>是</t>
   </si>
   <si>
-    <t>3298694232944009978</t>
-  </si>
-  <si>
-    <t>tb062516175225</t>
-  </si>
-  <si>
-    <t>极兔速递 JT5480183168323</t>
-  </si>
-  <si>
-    <t>振鸿</t>
-  </si>
-  <si>
-    <t>3297697322235106367</t>
-  </si>
-  <si>
-    <t>只能一年改一次</t>
-  </si>
-  <si>
-    <t>顺丰速运 SF0225523824581</t>
-  </si>
-  <si>
-    <t>5111273016030019324</t>
-  </si>
-  <si>
-    <t>jay_89757</t>
-  </si>
-  <si>
-    <t>顺丰速运 SF0226053710872</t>
-  </si>
-  <si>
-    <t>0427物流已更新到潮州</t>
-  </si>
-  <si>
-    <t>3297183962088001079</t>
-  </si>
-  <si>
-    <t>淡杰橙</t>
-  </si>
-  <si>
-    <t>申通快递 772061019165423</t>
-  </si>
-  <si>
-    <t>3297702000559001192</t>
-  </si>
-  <si>
-    <t>瞳孔中的水平线</t>
-  </si>
-  <si>
-    <t>中通快递 73705853678251</t>
-  </si>
-  <si>
-    <t>4502308394121050815</t>
-  </si>
-  <si>
-    <t>青晕晕</t>
-  </si>
-  <si>
-    <t>申通快递 772060951098059</t>
-  </si>
-  <si>
-    <t>3297897193516006882</t>
-  </si>
-  <si>
-    <t>黄昏光影</t>
-  </si>
-  <si>
-    <t>申通快递 772060984991552</t>
+    <t>5111094925001027547</t>
+  </si>
+  <si>
+    <t>tb942192175</t>
+  </si>
+  <si>
+    <t>极兔速递 JT3161329705289</t>
+  </si>
+  <si>
+    <t>0429物流已更新到潮州</t>
+  </si>
+  <si>
+    <t>5112297722999098522</t>
+  </si>
+  <si>
+    <t>t_1484586471144_0593</t>
+  </si>
+  <si>
+    <t>顺丰速运 SF5131080598864</t>
   </si>
   <si>
     <r>
-      <t>5110974722843028333</t>
+      <t>3297745059469031588</t>
     </r>
     <r>
       <rPr>
@@ -202,6 +175,171 @@
         <rFont val="PingFang SC"/>
         <charset val="134"/>
       </rPr>
+      <t>3298360800888004760</t>
+    </r>
+  </si>
+  <si>
+    <t>hsinhsia820</t>
+  </si>
+  <si>
+    <t>顺丰速运 SF5131064721716</t>
+  </si>
+  <si>
+    <t>5111927029757048016</t>
+  </si>
+  <si>
+    <t>占明1030</t>
+  </si>
+  <si>
+    <t>申通快递 772061112069930</t>
+  </si>
+  <si>
+    <t>3297901010220007689</t>
+  </si>
+  <si>
+    <t>花花花啊啊m</t>
+  </si>
+  <si>
+    <t>申通快递 772061066393190</t>
+  </si>
+  <si>
+    <t>0428物流未更新到潮州</t>
+  </si>
+  <si>
+    <t>5112077292914061845</t>
+  </si>
+  <si>
+    <t>bry168</t>
+  </si>
+  <si>
+    <t>顺丰速运 SF5131942141115</t>
+  </si>
+  <si>
+    <t>3298257517445020082</t>
+  </si>
+  <si>
+    <t>跨海_高速</t>
+  </si>
+  <si>
+    <t>申通快递 772061046443705</t>
+  </si>
+  <si>
+    <t>0428物流已更新到潮州</t>
+  </si>
+  <si>
+    <t>5111854671699037843</t>
+  </si>
+  <si>
+    <t>旧金山0121</t>
+  </si>
+  <si>
+    <t>顺丰速运 SF0221623837115</t>
+  </si>
+  <si>
+    <t>瑞丰</t>
+  </si>
+  <si>
+    <t>5112421778175023237</t>
+  </si>
+  <si>
+    <t>zhuoyingpeng</t>
+  </si>
+  <si>
+    <t>顺丰速运，SF0228083759096</t>
+  </si>
+  <si>
+    <t>0427物流未更新到潮州</t>
+  </si>
+  <si>
+    <t>3298694232944009978</t>
+  </si>
+  <si>
+    <t>tb062516175225</t>
+  </si>
+  <si>
+    <t>极兔速递 JT5480183168323</t>
+  </si>
+  <si>
+    <t>振鸿</t>
+  </si>
+  <si>
+    <t>3297697322235106367</t>
+  </si>
+  <si>
+    <t>只能一年改一次</t>
+  </si>
+  <si>
+    <t>顺丰速运 SF0225523824581</t>
+  </si>
+  <si>
+    <t>5111273016030019324</t>
+  </si>
+  <si>
+    <t>jay_89757</t>
+  </si>
+  <si>
+    <t>顺丰速运 SF0226053710872</t>
+  </si>
+  <si>
+    <t>0427物流已更新到潮州</t>
+  </si>
+  <si>
+    <t>3297183962088001079</t>
+  </si>
+  <si>
+    <t>淡杰橙</t>
+  </si>
+  <si>
+    <t>申通快递 772061019165423</t>
+  </si>
+  <si>
+    <t>3297702000559001192</t>
+  </si>
+  <si>
+    <t>瞳孔中的水平线</t>
+  </si>
+  <si>
+    <t>中通快递 73705853678251</t>
+  </si>
+  <si>
+    <t>4502308394121050815</t>
+  </si>
+  <si>
+    <t>青晕晕</t>
+  </si>
+  <si>
+    <t>申通快递 772060951098059</t>
+  </si>
+  <si>
+    <t>3297897193516006882</t>
+  </si>
+  <si>
+    <t>黄昏光影</t>
+  </si>
+  <si>
+    <t>申通快递 772060984991552</t>
+  </si>
+  <si>
+    <r>
+      <t>5110974722843028333</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="PingFang SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="PingFang SC"/>
+        <charset val="134"/>
+      </rPr>
       <t>5111262469540028333</t>
     </r>
   </si>
@@ -254,6 +392,9 @@
     <t>t_1500087239816_0842</t>
   </si>
   <si>
+    <t>中通快递 73706176688459</t>
+  </si>
+  <si>
     <t>5111067926075068027</t>
   </si>
   <si>
@@ -273,6 +414,21 @@
   </si>
   <si>
     <t>申通快递 772060851430833</t>
+  </si>
+  <si>
+    <t>3退1</t>
+  </si>
+  <si>
+    <t>3297137523297135890</t>
+  </si>
+  <si>
+    <t>yuanjun28101</t>
+  </si>
+  <si>
+    <t>540.12</t>
+  </si>
+  <si>
+    <t>顺丰速运 SF5199883700753</t>
   </si>
 </sst>
 </file>
@@ -286,7 +442,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -318,6 +474,12 @@
       <sz val="9"/>
       <color rgb="FFDE3C36"/>
       <name val="PingFang SC"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFDE3C36"/>
+      <name val="Microsoft YaHei"/>
       <charset val="134"/>
     </font>
     <font>
@@ -841,137 +1003,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -985,84 +1147,75 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1452,7 +1605,7 @@
     </row>
     <row r="2" ht="15" spans="2:12">
       <c r="B2" s="2">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>9</v>
@@ -1465,843 +1618,1063 @@
       </c>
       <c r="F2"/>
       <c r="G2" s="6">
-        <v>694.2</v>
+        <v>827.12</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="5"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="8"/>
+      <c r="I2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="8"/>
+      <c r="K2" s="9"/>
     </row>
     <row r="3" ht="15" spans="2:12">
       <c r="B3" s="2">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F3"/>
       <c r="G3" s="6">
-        <v>205.12</v>
+        <v>776.7</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" s="5"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="9"/>
+        <v>17</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="8"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="10"/>
     </row>
     <row r="4" ht="15" spans="2:12">
       <c r="B4" s="2">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>19</v>
       </c>
       <c r="F4"/>
       <c r="G4" s="6">
-        <v>103.14</v>
+        <v>1919.67</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" s="7"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="9"/>
+        <v>20</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="8"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="10"/>
     </row>
     <row r="5" ht="15" spans="2:12">
       <c r="B5" s="2">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="F5"/>
       <c r="G5" s="6">
-        <v>1284</v>
+        <v>163.12</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5" s="7"/>
-      <c r="K5" s="8"/>
+        <v>23</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="8"/>
+      <c r="K5" s="9"/>
     </row>
     <row r="6" ht="15" spans="2:12">
       <c r="B6" s="2">
-        <v>46139</v>
+        <v>46141</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="11" t="s">
         <v>24</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F6"/>
       <c r="G6" s="6">
-        <v>1299</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" s="5" t="s">
+        <v>1262.45</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="I6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="K6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="9"/>
     </row>
     <row r="7" ht="15" spans="2:12">
       <c r="B7" s="2">
-        <v>46139</v>
+        <v>46141</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F7"/>
       <c r="G7" s="6">
-        <v>1290.35</v>
-      </c>
-      <c r="H7" s="11" t="s">
+        <v>927.01</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7" s="7"/>
-      <c r="K7" s="8"/>
+      <c r="I7" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" s="8"/>
+      <c r="K7" s="9"/>
     </row>
     <row r="8" ht="15" spans="2:12">
       <c r="B8" s="2">
-        <v>46139</v>
+        <v>46141</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="E8" s="7" t="s">
         <v>32</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>33</v>
       </c>
       <c r="F8"/>
       <c r="G8" s="6">
-        <v>827.12</v>
+        <v>1284.2</v>
       </c>
       <c r="H8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J8" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J8" s="7"/>
-      <c r="K8" s="8"/>
+      <c r="K8" s="9"/>
     </row>
     <row r="9" ht="15" spans="2:12">
       <c r="B9" s="2">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="7" t="s">
         <v>36</v>
       </c>
       <c r="F9"/>
       <c r="G9" s="6">
-        <v>214.4</v>
+        <v>110</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="J9" s="7"/>
-      <c r="K9" s="8"/>
+      <c r="J9" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="K9" s="9"/>
     </row>
     <row r="10" ht="15" spans="2:12">
       <c r="B10" s="2">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="7" t="s">
         <v>40</v>
       </c>
       <c r="F10"/>
       <c r="G10" s="6">
-        <v>163.12</v>
+        <v>1699</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="I10" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J10" s="7"/>
-      <c r="K10" s="8"/>
-    </row>
-    <row r="11" ht="15" spans="2:12">
+      <c r="I10" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J10" s="8"/>
+      <c r="K10" s="9"/>
+    </row>
+    <row r="11" ht="22.8" spans="2:12">
       <c r="B11" s="2">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="7" t="s">
         <v>43</v>
       </c>
       <c r="F11"/>
       <c r="G11" s="6">
-        <v>159</v>
+        <v>3736.84</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="I11" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="J11" s="7"/>
-      <c r="K11" s="8"/>
+      <c r="I11" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J11" s="8"/>
+      <c r="K11" s="9"/>
     </row>
     <row r="12" ht="15" spans="2:12">
       <c r="B12" s="2">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="7" t="s">
         <v>46</v>
       </c>
       <c r="F12"/>
       <c r="G12" s="6">
-        <v>821.34</v>
+        <v>526.04</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="I12" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="J12" s="7"/>
-      <c r="K12" s="8"/>
+      <c r="I12" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J12" s="8"/>
+      <c r="K12" s="9"/>
       <c r="L12" s="12"/>
     </row>
     <row r="13" ht="15" spans="2:12">
       <c r="B13" s="2">
-        <v>46138</v>
+        <v>46140</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="7" t="s">
         <v>49</v>
       </c>
       <c r="F13"/>
       <c r="G13" s="6">
-        <v>250.14</v>
+        <v>694.2</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="I13" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="J13" s="7"/>
-      <c r="K13" s="8"/>
-    </row>
-    <row r="14" ht="22.8" spans="2:12">
+      <c r="I13" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="J13" s="8"/>
+      <c r="K13" s="9"/>
+    </row>
+    <row r="14" ht="15" spans="2:12">
       <c r="B14" s="2">
-        <v>46138</v>
+        <v>46140</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>52</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="F14"/>
       <c r="G14" s="6">
-        <v>2206.13</v>
+        <v>205.12</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="J14" s="7"/>
-      <c r="K14" s="8"/>
+        <v>54</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="K14" s="9"/>
     </row>
     <row r="15" ht="15" spans="2:12">
       <c r="B15" s="2">
-        <v>46138</v>
+        <v>46140</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E15" s="5" t="s">
         <v>55</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="F15"/>
       <c r="G15" s="6">
-        <v>1037.2</v>
+        <v>103.14</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="J15" s="7"/>
-      <c r="K15" s="8"/>
+        <v>57</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="K15" s="9"/>
     </row>
     <row r="16" spans="2:12">
       <c r="B16" s="13">
-        <v>46138</v>
+        <v>46140</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F16"/>
       <c r="G16" s="17">
-        <v>929</v>
+        <v>1284</v>
       </c>
       <c r="H16" s="15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="J16" s="18" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="K16" s="19"/>
     </row>
-    <row r="17" ht="15" spans="2:11">
-      <c r="B17" s="2">
-        <v>46138</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>61</v>
+    <row r="17" spans="2:11">
+      <c r="B17" s="13">
+        <v>46139</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>64</v>
       </c>
       <c r="F17"/>
-      <c r="G17" s="6">
-        <v>2799</v>
-      </c>
-      <c r="H17" s="11" t="s">
+      <c r="G17" s="17">
+        <v>1299</v>
+      </c>
+      <c r="H17" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="I17" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J17" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="K17" s="19"/>
+    </row>
+    <row r="18" ht="15" spans="2:11">
+      <c r="B18" s="13">
+        <v>46139</v>
+      </c>
+      <c r="C18" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="I17" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="J17" s="7"/>
-      <c r="K17" s="8"/>
-    </row>
-    <row r="18" spans="2:11">
-      <c r="B18" s="13">
-        <v>46138</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>63</v>
+      <c r="D18" s="20" t="s">
+        <v>67</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F18"/>
       <c r="G18" s="17">
-        <v>165</v>
-      </c>
-      <c r="H18" s="15" t="s">
-        <v>65</v>
+        <v>1290.35</v>
+      </c>
+      <c r="H18" s="17" t="s">
+        <v>69</v>
       </c>
       <c r="I18" s="16" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="J18" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="K18" s="19"/>
+        <v>34</v>
+      </c>
+      <c r="K18" s="9"/>
     </row>
     <row r="19" ht="15" spans="2:11">
-      <c r="B19" s="2">
-        <v>46137</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>67</v>
+      <c r="B19" s="13">
+        <v>46139</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>72</v>
       </c>
       <c r="F19"/>
-      <c r="G19" s="6">
-        <v>164.4</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="I19" s="5"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="8"/>
-    </row>
-    <row r="20" ht="15" spans="2:11">
-      <c r="B20" s="2">
-        <v>46137</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>69</v>
+      <c r="G19" s="17">
+        <v>827.12</v>
+      </c>
+      <c r="H19" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="I19" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="J19" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="K19" s="9"/>
+    </row>
+    <row r="20" spans="2:11">
+      <c r="B20" s="13">
+        <v>46139</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>75</v>
       </c>
       <c r="F20"/>
-      <c r="G20" s="6">
-        <v>943.8</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="J20" s="7"/>
-      <c r="K20" s="8"/>
+      <c r="G20" s="17">
+        <v>214.4</v>
+      </c>
+      <c r="H20" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="I20" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="J20" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="K20" s="19"/>
     </row>
     <row r="21" ht="15" spans="2:11">
       <c r="B21" s="2">
+        <v>46139</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F21"/>
+      <c r="G21" s="6">
+        <v>163.12</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="K21" s="9"/>
+    </row>
+    <row r="22" ht="15" spans="2:11">
+      <c r="B22" s="2">
+        <v>46139</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="F22"/>
+      <c r="G22" s="6">
+        <v>159</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="K22" s="9"/>
+    </row>
+    <row r="23" ht="15" spans="2:11">
+      <c r="B23" s="2">
+        <v>46139</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F23"/>
+      <c r="G23" s="6">
+        <v>821.34</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="K23" s="9"/>
+    </row>
+    <row r="24" ht="15" spans="2:11">
+      <c r="B24" s="2">
+        <v>46138</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="F24"/>
+      <c r="G24" s="6">
+        <v>250.14</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="K24" s="9"/>
+    </row>
+    <row r="25" ht="22.8" spans="2:11">
+      <c r="B25" s="13">
+        <v>46138</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="F25"/>
+      <c r="G25" s="17">
+        <v>2206.13</v>
+      </c>
+      <c r="H25" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="I25" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J25" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="K25" s="19"/>
+    </row>
+    <row r="26" spans="2:11">
+      <c r="B26" s="13">
+        <v>46138</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="E26" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="F26"/>
+      <c r="G26" s="17">
+        <v>1037.2</v>
+      </c>
+      <c r="H26" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="I26" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J26" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="K26" s="19"/>
+    </row>
+    <row r="27" spans="2:11">
+      <c r="B27" s="13">
+        <v>46138</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="E27" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="F27"/>
+      <c r="G27" s="17">
+        <v>929</v>
+      </c>
+      <c r="H27" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="I27" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J27" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="K27" s="19"/>
+    </row>
+    <row r="28" ht="15" spans="2:11">
+      <c r="B28" s="2">
+        <v>46138</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="F28"/>
+      <c r="G28" s="6">
+        <v>2799</v>
+      </c>
+      <c r="H28" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="J28" s="8"/>
+      <c r="K28" s="9"/>
+    </row>
+    <row r="29" spans="2:11">
+      <c r="B29" s="13">
+        <v>46138</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="F29"/>
+      <c r="G29" s="17">
+        <v>165</v>
+      </c>
+      <c r="H29" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="I29" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="J29" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="K29" s="19"/>
+    </row>
+    <row r="30" ht="15" spans="2:11">
+      <c r="B30" s="2">
         <v>46137</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F21"/>
-      <c r="G21" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="H21" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="J21" s="7"/>
-      <c r="K21" s="8"/>
-    </row>
-    <row r="22" ht="15" spans="2:11">
-      <c r="B22" s="20"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="23"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="23"/>
-      <c r="J22" s="24"/>
-      <c r="K22" s="25"/>
-    </row>
-    <row r="23" spans="2:11">
-      <c r="B23" s="26"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="9"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="29"/>
-      <c r="K23" s="30"/>
-    </row>
-    <row r="24" spans="2:11">
-      <c r="B24" s="26"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="9"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="28"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="29"/>
-      <c r="K24" s="30"/>
-    </row>
-    <row r="25" spans="2:11">
-      <c r="B25" s="26"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="9"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="29"/>
-      <c r="K25" s="30"/>
-    </row>
-    <row r="26" spans="2:11">
-      <c r="B26" s="26"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="9"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="29"/>
-      <c r="K26" s="30"/>
-    </row>
-    <row r="27" spans="2:11">
-      <c r="B27" s="26"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="9"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="29"/>
-      <c r="K27" s="30"/>
-    </row>
-    <row r="28" ht="15" spans="2:11">
-      <c r="B28" s="26"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="9"/>
-      <c r="G28" s="28"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="29"/>
-      <c r="K28" s="25"/>
-    </row>
-    <row r="29" ht="15" spans="2:11">
-      <c r="B29" s="26"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="29"/>
-      <c r="K29" s="25"/>
-    </row>
-    <row r="30" spans="2:11">
-      <c r="B30" s="26"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="9"/>
-      <c r="G30" s="31"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="29"/>
-      <c r="K30" s="30"/>
-    </row>
-    <row r="31" spans="2:11">
-      <c r="B31" s="26"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="9"/>
-      <c r="G31" s="31"/>
-      <c r="H31" s="28"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="29"/>
-      <c r="K31" s="30"/>
-    </row>
-    <row r="32" spans="2:11">
-      <c r="B32" s="26"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="9"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="29"/>
-      <c r="K32" s="30"/>
+      <c r="C30" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="F30"/>
+      <c r="G30" s="6">
+        <v>164.4</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="I30" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J30" s="8"/>
+      <c r="K30" s="9"/>
+    </row>
+    <row r="31" ht="15" spans="2:11">
+      <c r="B31" s="13">
+        <v>46137</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="F31"/>
+      <c r="G31" s="17">
+        <v>943.8</v>
+      </c>
+      <c r="H31" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="I31" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J31" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="K31" s="9"/>
+    </row>
+    <row r="32" ht="15" spans="2:11">
+      <c r="B32" s="2">
+        <v>46137</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="F32"/>
+      <c r="G32" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="H32" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="I32" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="K32" s="9"/>
     </row>
     <row r="33" spans="2:11">
-      <c r="B33" s="26"/>
-      <c r="C33" s="27"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="9"/>
-      <c r="G33" s="31"/>
-      <c r="H33" s="28"/>
-      <c r="I33" s="9"/>
-      <c r="J33" s="29"/>
-      <c r="K33" s="30"/>
+      <c r="B33" s="13">
+        <v>46137</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E33" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="F33"/>
+      <c r="G33" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="H33" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="I33" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="J33" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="K33" s="19"/>
     </row>
     <row r="34" spans="2:11">
-      <c r="B34" s="26"/>
-      <c r="C34" s="27"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="9"/>
-      <c r="G34" s="31"/>
-      <c r="H34" s="28"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="29"/>
-      <c r="K34" s="30"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="23"/>
+      <c r="D34" s="24"/>
+      <c r="E34" s="10"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="24"/>
+      <c r="I34" s="10"/>
+      <c r="J34" s="26"/>
+      <c r="K34" s="27"/>
     </row>
     <row r="35" spans="2:11">
-      <c r="B35" s="26"/>
-      <c r="C35" s="27"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="9"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="28"/>
-      <c r="I35" s="9"/>
-      <c r="J35" s="29"/>
-      <c r="K35" s="30"/>
+      <c r="B35" s="22"/>
+      <c r="C35" s="23"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="10"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="24"/>
+      <c r="I35" s="10"/>
+      <c r="J35" s="26"/>
+      <c r="K35" s="27"/>
     </row>
     <row r="36" ht="15" spans="2:11">
-      <c r="B36" s="26"/>
-      <c r="C36" s="27"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="9"/>
-      <c r="G36" s="31"/>
-      <c r="H36" s="28"/>
-      <c r="I36" s="9"/>
-      <c r="J36" s="29"/>
-      <c r="K36" s="25"/>
+      <c r="B36" s="22"/>
+      <c r="C36" s="23"/>
+      <c r="D36" s="24"/>
+      <c r="E36" s="10"/>
+      <c r="G36" s="25"/>
+      <c r="H36" s="24"/>
+      <c r="I36" s="10"/>
+      <c r="J36" s="26"/>
+      <c r="K36" s="28"/>
     </row>
     <row r="37" ht="15" spans="2:11">
-      <c r="B37" s="26"/>
-      <c r="C37" s="27"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="9"/>
-      <c r="G37" s="31"/>
-      <c r="H37" s="31"/>
-      <c r="I37" s="9"/>
-      <c r="J37" s="29"/>
-      <c r="K37" s="25"/>
+      <c r="B37" s="22"/>
+      <c r="C37" s="23"/>
+      <c r="D37" s="24"/>
+      <c r="E37" s="10"/>
+      <c r="G37" s="25"/>
+      <c r="H37" s="25"/>
+      <c r="I37" s="10"/>
+      <c r="J37" s="26"/>
+      <c r="K37" s="28"/>
     </row>
     <row r="38" ht="15" spans="2:11">
-      <c r="B38" s="26"/>
-      <c r="C38" s="27"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="9"/>
-      <c r="G38" s="31"/>
-      <c r="H38" s="28"/>
-      <c r="I38" s="9"/>
-      <c r="J38" s="29"/>
-      <c r="K38" s="25"/>
+      <c r="B38" s="22"/>
+      <c r="C38" s="23"/>
+      <c r="D38" s="24"/>
+      <c r="E38" s="10"/>
+      <c r="G38" s="25"/>
+      <c r="H38" s="24"/>
+      <c r="I38" s="10"/>
+      <c r="J38" s="26"/>
+      <c r="K38" s="28"/>
     </row>
     <row r="39" spans="2:11">
-      <c r="B39" s="26"/>
-      <c r="C39" s="27"/>
-      <c r="D39" s="28"/>
-      <c r="E39" s="9"/>
-      <c r="G39" s="31"/>
-      <c r="H39" s="28"/>
-      <c r="I39" s="9"/>
-      <c r="J39" s="29"/>
-      <c r="K39" s="30"/>
+      <c r="B39" s="22"/>
+      <c r="C39" s="23"/>
+      <c r="D39" s="24"/>
+      <c r="E39" s="10"/>
+      <c r="G39" s="25"/>
+      <c r="H39" s="24"/>
+      <c r="I39" s="10"/>
+      <c r="J39" s="26"/>
+      <c r="K39" s="27"/>
     </row>
     <row r="40" ht="15" spans="2:11">
-      <c r="B40" s="26"/>
-      <c r="C40" s="27"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="9"/>
-      <c r="G40" s="31"/>
-      <c r="H40" s="28"/>
-      <c r="I40" s="9"/>
-      <c r="J40" s="29"/>
-      <c r="K40" s="25"/>
+      <c r="B40" s="22"/>
+      <c r="C40" s="23"/>
+      <c r="D40" s="24"/>
+      <c r="E40" s="10"/>
+      <c r="G40" s="25"/>
+      <c r="H40" s="24"/>
+      <c r="I40" s="10"/>
+      <c r="J40" s="26"/>
+      <c r="K40" s="28"/>
     </row>
     <row r="41" ht="15" spans="2:11">
-      <c r="B41" s="26"/>
-      <c r="C41" s="27"/>
-      <c r="D41" s="28"/>
-      <c r="E41" s="9"/>
-      <c r="G41" s="31"/>
-      <c r="H41" s="28"/>
-      <c r="I41" s="9"/>
-      <c r="J41" s="29"/>
-      <c r="K41" s="25"/>
+      <c r="B41" s="22"/>
+      <c r="C41" s="23"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="10"/>
+      <c r="G41" s="25"/>
+      <c r="H41" s="24"/>
+      <c r="I41" s="10"/>
+      <c r="J41" s="26"/>
+      <c r="K41" s="28"/>
     </row>
     <row r="42" ht="15" spans="2:11">
-      <c r="B42" s="26"/>
-      <c r="C42" s="27"/>
-      <c r="D42" s="28"/>
-      <c r="E42" s="9"/>
-      <c r="G42" s="31"/>
-      <c r="H42" s="28"/>
-      <c r="I42" s="9"/>
-      <c r="J42" s="29"/>
-      <c r="K42" s="25"/>
+      <c r="B42" s="22"/>
+      <c r="C42" s="23"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="10"/>
+      <c r="G42" s="25"/>
+      <c r="H42" s="24"/>
+      <c r="I42" s="10"/>
+      <c r="J42" s="26"/>
+      <c r="K42" s="28"/>
     </row>
     <row r="43" spans="2:11">
-      <c r="B43" s="26"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="9"/>
-      <c r="G43" s="31"/>
-      <c r="H43" s="28"/>
-      <c r="I43" s="9"/>
-      <c r="J43" s="29"/>
-      <c r="K43" s="30"/>
+      <c r="B43" s="22"/>
+      <c r="C43" s="23"/>
+      <c r="D43" s="24"/>
+      <c r="E43" s="10"/>
+      <c r="G43" s="25"/>
+      <c r="H43" s="24"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="26"/>
+      <c r="K43" s="27"/>
     </row>
     <row r="44" spans="2:11">
-      <c r="B44" s="26"/>
-      <c r="C44" s="27"/>
-      <c r="D44" s="28"/>
-      <c r="E44" s="9"/>
-      <c r="G44" s="31"/>
-      <c r="H44" s="28"/>
-      <c r="I44" s="9"/>
-      <c r="J44" s="29"/>
-      <c r="K44" s="30"/>
+      <c r="B44" s="22"/>
+      <c r="C44" s="23"/>
+      <c r="D44" s="24"/>
+      <c r="E44" s="10"/>
+      <c r="G44" s="25"/>
+      <c r="H44" s="24"/>
+      <c r="I44" s="10"/>
+      <c r="J44" s="26"/>
+      <c r="K44" s="27"/>
     </row>
     <row r="45" ht="15" spans="2:11">
-      <c r="B45" s="26"/>
-      <c r="C45" s="27"/>
-      <c r="D45" s="28"/>
-      <c r="E45" s="9"/>
-      <c r="G45" s="32"/>
-      <c r="H45" s="28"/>
-      <c r="I45" s="9"/>
-      <c r="J45" s="29"/>
-      <c r="K45" s="25"/>
+      <c r="B45" s="22"/>
+      <c r="C45" s="23"/>
+      <c r="D45" s="24"/>
+      <c r="E45" s="10"/>
+      <c r="G45" s="29"/>
+      <c r="H45" s="24"/>
+      <c r="I45" s="10"/>
+      <c r="J45" s="26"/>
+      <c r="K45" s="28"/>
     </row>
     <row r="46" ht="15" spans="2:11">
-      <c r="B46" s="26"/>
-      <c r="C46" s="27"/>
-      <c r="D46" s="28"/>
-      <c r="E46" s="9"/>
-      <c r="G46" s="32"/>
-      <c r="H46" s="28"/>
-      <c r="I46" s="9"/>
-      <c r="J46" s="29"/>
-      <c r="K46" s="25"/>
+      <c r="B46" s="22"/>
+      <c r="C46" s="23"/>
+      <c r="D46" s="24"/>
+      <c r="E46" s="10"/>
+      <c r="G46" s="29"/>
+      <c r="H46" s="24"/>
+      <c r="I46" s="10"/>
+      <c r="J46" s="26"/>
+      <c r="K46" s="28"/>
     </row>
     <row r="47" spans="2:11">
-      <c r="B47" s="26"/>
-      <c r="C47" s="27"/>
-      <c r="D47" s="28"/>
-      <c r="E47" s="9"/>
-      <c r="G47" s="31"/>
-      <c r="H47" s="28"/>
-      <c r="I47" s="9"/>
-      <c r="J47" s="29"/>
-      <c r="K47" s="30"/>
+      <c r="B47" s="22"/>
+      <c r="C47" s="23"/>
+      <c r="D47" s="24"/>
+      <c r="E47" s="10"/>
+      <c r="G47" s="25"/>
+      <c r="H47" s="24"/>
+      <c r="I47" s="10"/>
+      <c r="J47" s="26"/>
+      <c r="K47" s="27"/>
     </row>
     <row r="48" spans="2:11">
-      <c r="B48" s="26"/>
-      <c r="C48" s="27"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="9"/>
-      <c r="G48" s="31"/>
-      <c r="H48" s="28"/>
-      <c r="I48" s="9"/>
-      <c r="J48" s="29"/>
-      <c r="K48" s="30"/>
+      <c r="B48" s="22"/>
+      <c r="C48" s="23"/>
+      <c r="D48" s="24"/>
+      <c r="E48" s="10"/>
+      <c r="G48" s="25"/>
+      <c r="H48" s="24"/>
+      <c r="I48" s="10"/>
+      <c r="J48" s="26"/>
+      <c r="K48" s="27"/>
     </row>
     <row r="49" spans="2:11">
-      <c r="B49" s="26"/>
-      <c r="C49" s="27"/>
-      <c r="D49" s="28"/>
-      <c r="E49" s="9"/>
-      <c r="G49" s="31"/>
-      <c r="H49" s="28"/>
-      <c r="I49" s="9"/>
-      <c r="J49" s="29"/>
-      <c r="K49" s="30"/>
+      <c r="B49" s="22"/>
+      <c r="C49" s="23"/>
+      <c r="D49" s="24"/>
+      <c r="E49" s="10"/>
+      <c r="G49" s="25"/>
+      <c r="H49" s="24"/>
+      <c r="I49" s="10"/>
+      <c r="J49" s="26"/>
+      <c r="K49" s="27"/>
     </row>
     <row r="50" ht="15" spans="2:11">
-      <c r="B50" s="26"/>
-      <c r="C50" s="27"/>
-      <c r="D50" s="28"/>
-      <c r="E50" s="9"/>
-      <c r="G50" s="31"/>
-      <c r="H50" s="28"/>
-      <c r="I50" s="9"/>
-      <c r="J50" s="29"/>
-      <c r="K50" s="25"/>
+      <c r="B50" s="22"/>
+      <c r="C50" s="23"/>
+      <c r="D50" s="24"/>
+      <c r="E50" s="10"/>
+      <c r="G50" s="25"/>
+      <c r="H50" s="24"/>
+      <c r="I50" s="10"/>
+      <c r="J50" s="26"/>
+      <c r="K50" s="28"/>
     </row>
     <row r="51" spans="2:11">
-      <c r="B51" s="26"/>
-      <c r="C51" s="27"/>
-      <c r="D51" s="28"/>
-      <c r="E51" s="9"/>
-      <c r="G51" s="31"/>
-      <c r="H51" s="28"/>
-      <c r="I51" s="9"/>
-      <c r="J51" s="29"/>
-      <c r="K51" s="30"/>
+      <c r="B51" s="22"/>
+      <c r="C51" s="23"/>
+      <c r="D51" s="24"/>
+      <c r="E51" s="10"/>
+      <c r="G51" s="25"/>
+      <c r="H51" s="24"/>
+      <c r="I51" s="10"/>
+      <c r="J51" s="26"/>
+      <c r="K51" s="27"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
